--- a/output/pdf_financials_xlsx/DII.A.xlsx
+++ b/output/pdf_financials_xlsx/DII.A.xlsx
@@ -7066,10 +7066,10 @@
         <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>5.997</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="113">
@@ -52762,7 +52762,11 @@
           <t>Proceeds on disposals of property, plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -52861,7 +52865,11 @@
           <t>Additions to intangible assets (Notes 11 and 27)</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -55058,7 +55066,11 @@
           <t>Additions to intangible assets (Notes 11 and 26)</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -59058,7 +59070,11 @@
           <t>Additions to intangible assets (Notes 12 and 27)</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -61535,7 +61551,11 @@
           <t>Additions to intangible assets (Notes 13 and 29)</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -63291,7 +63311,11 @@
           <t>Additions to intangible assets (Notes 11 and 29)</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -68891,7 +68915,11 @@
           <t>Additions to intangible assets (Notes 12 and 30)</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr">
         <is>
           <t>-</t>
@@ -77554,7 +77582,11 @@
           <t>Additions to intangible assets (Notes 9 and 26)</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E701" t="inlineStr">
         <is>
           <t>-</t>
@@ -80437,7 +80469,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DII.A.xlsx
+++ b/output/pdf_financials_xlsx/DII.A.xlsx
@@ -4663,22 +4663,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>40.58</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>29.546</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>33.293</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>37.064</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>36.012</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>30.226</v>
       </c>
     </row>
     <row r="71">
@@ -4721,22 +4721,22 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>40.58</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>29.546</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>33.293</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>37.064</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>36.012</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>30.226</v>
       </c>
     </row>
     <row r="72">
@@ -4953,22 +4953,22 @@
         <v>545.571</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>198.815</v>
+        <v>158.235</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>122.027</v>
+        <v>92.48099999999999</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>95.464</v>
+        <v>62.171</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>108.385</v>
+        <v>71.321</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>300.365</v>
+        <v>264.353</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>106.287</v>
+        <v>76.06100000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5243,22 +5243,22 @@
         <v>0.7521368845110075</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>1.10434771213443</v>
+        <v>1.180316605699352</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>1.089650319829424</v>
+        <v>1.152648187633262</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>1.374139231141337</v>
+        <v>1.492558973337507</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>1.551272351825974</v>
+        <v>1.716219704319499</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>7.696533232090738</v>
+        <v>8.551052369314002</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>-3.902209244669715</v>
+        <v>-4.235259765302187</v>
       </c>
     </row>
     <row r="81">
@@ -6673,55 +6673,55 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-78.50700000000001</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>47.659</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-97.13500000000001</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>22.544</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-76.72</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>8.933999999999999</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-50.491</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-46.327</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>75.254</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-65.08499999999999</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>31.856</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-21.154</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-26.403</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-42.079</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>86.59</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>54.451</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>3.256</v>
       </c>
     </row>
     <row r="107">
@@ -6798,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>1.372</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0</v>
+        <v>45.302</v>
       </c>
       <c r="R108" s="3" t="n">
         <v>0</v>
@@ -7082,40 +7082,40 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-21.661</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-36.319</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0</v>
+        <v>-14.819</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>-71.92400000000001</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0</v>
+        <v>-170.551</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0</v>
+        <v>-2.326</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0</v>
+        <v>5.475</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="3" t="n">
-        <v>0</v>
+        <v>-2.953</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>0</v>
+        <v>-0.162</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>0</v>
+        <v>-10.893</v>
       </c>
       <c r="O113" s="3" t="n">
         <v>0</v>
@@ -7548,19 +7548,19 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-10.504</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-17.277</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-17.399</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-17.812</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.321</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.499</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
@@ -7593,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-1.094</v>
       </c>
     </row>
     <row r="122">
@@ -7661,37 +7661,37 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>266.297</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>32.883</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>18.195</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>249.033</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>32.107</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>217.36</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>18.739</v>
       </c>
       <c r="M123" s="3" t="n">
         <v>0</v>
@@ -7777,37 +7777,37 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-62.4</v>
+        <v>203.897</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>-110.522</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-220.491</v>
+        <v>-20.491</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>-14.855</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-16.767</v>
+        <v>16.116</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-14.243</v>
+        <v>3.952</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-26.926</v>
+        <v>222.107</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-64.134</v>
+        <v>-32.027</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-187.189</v>
+        <v>30.171</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-29.821</v>
+        <v>-11.082</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>-162.361</v>
@@ -10246,7 +10246,11 @@
           <t>Lease liabilities (Note 10 b))</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -21166,7 +21170,11 @@
           <t>Lease liabilities (Note 11)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -24695,7 +24703,11 @@
           <t>Lease liabilities (Note 12)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -50242,7 +50254,11 @@
           <t>Impairment loss on goodwill (Notes 12 and 29)</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -51121,7 +51137,11 @@
           <t>Net changes in balances related to operations (Note 27)</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -52366,7 +52386,11 @@
           <t>Shares repurchased (Note 21)</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -53605,7 +53629,11 @@
           <t>Impairment loss on goodwill (Notes 12 and 28)</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -54199,7 +54227,11 @@
           <t>Net changes in balances related to operations (Note 26)</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -56862,7 +56894,11 @@
           <t>Shares repurchased (Note 20)</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -57573,7 +57609,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -58767,7 +58807,11 @@
           <t>Acquisition of business (Note 9)</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -60369,7 +60413,11 @@
           <t>Net changes in balances related to operations (Note 29)</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -61266,7 +61314,11 @@
           <t>Acquisition of businesses</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -62539,7 +62591,11 @@
           <t>Increase of long-term debt</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E550" s="5" t="n">
         <v>266.297</v>
       </c>
@@ -63008,7 +63064,11 @@
           <t>Acquisition of a business (Note 29)</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
@@ -63903,7 +63963,11 @@
           <t>Net changes in balances related to operations (Note 30)</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -64303,7 +64367,11 @@
           <t>Increase of long-term debt</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
@@ -64606,7 +64674,11 @@
           <t>Acquisition of businesses (Note 30)</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -66713,7 +66785,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -67608,7 +67684,11 @@
           <t>Net changes in balances related to operations (Note 30)</t>
         </is>
       </c>
-      <c r="D601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E601" t="inlineStr">
         <is>
           <t>-</t>
@@ -69408,7 +69488,11 @@
           <t>Net Income (Loss)</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
@@ -70406,7 +70490,11 @@
           <t>Net changes in balances related to operations (Note 30)</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E629" t="inlineStr">
         <is>
           <t>-</t>
@@ -71210,7 +71298,11 @@
           <t>Share repurchase (Note 23)</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E637" t="inlineStr">
         <is>
           <t>-</t>
@@ -71612,7 +71704,11 @@
           <t>Acquisition of businesses (Notes 7 and 30)</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E641" t="inlineStr">
         <is>
           <t>-</t>
@@ -73602,7 +73698,11 @@
           <t>Net changes in balances related to operations (Note 30)</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
           <t>-</t>
@@ -74406,7 +74506,11 @@
           <t>Share repurchase (Note 23)</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -75107,7 +75211,11 @@
           <t>Impairment loss of goodwill (Note 10)</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr">
         <is>
           <t>-</t>
@@ -76089,7 +76197,11 @@
           <t>Net changes in balances related to operations (Note 26)</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
           <t>-</t>
@@ -76887,7 +76999,11 @@
           <t>Share repurchase (Note 19)</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
           <t>-</t>
@@ -77287,7 +77403,11 @@
           <t>Acquisition of businesses (Notes 4 and 26)</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
           <t>-</t>
@@ -77881,7 +78001,11 @@
           <t>Impairment losses of goodwill (Note 10)</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E704" t="inlineStr">
         <is>
           <t>-</t>
@@ -78180,7 +78304,11 @@
           <t>Net changes in non-cash balances related to operations (Note 26)</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E707" t="inlineStr">
         <is>
           <t>-</t>
@@ -78380,7 +78508,11 @@
           <t>Share repurchase (Note 19)</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E709" t="inlineStr">
         <is>
           <t>-</t>
@@ -78677,7 +78809,11 @@
           <t>Acquisition of business (Notes 4 and 26)</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>-</t>
@@ -79374,7 +79510,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E719" s="5" t="n">
         <v>2.156</v>
       </c>
@@ -79972,7 +80112,11 @@
           <t>Net changes in non-cash balances related to operations (Note 26)</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -80071,7 +80215,11 @@
           <t>Share repurchase (Note 17)</t>
         </is>
       </c>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
           <t>-</t>
@@ -81380,7 +81528,11 @@
           <t>Net changes in non-cash balances related to operations (Note 24)</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E739" s="5" t="n">
         <v>-78.50700000000001</v>
       </c>
@@ -81479,7 +81631,11 @@
           <t>Share repurchase (Note 16)</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E740" t="inlineStr">
         <is>
           <t>-</t>
